--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -501,130 +501,140 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>35640.50075139798</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>164694.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>200334.830751398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-06-30 (30 days)</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ethereum=25433093</t>
+          <t>2026-06-01 → 2026-06-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-03T07:02:13+00:00</t>
+          <t>ethereum=25433093</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:51:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>35640.50075139798</v>
+        <v>34311.83015664823</v>
       </c>
     </row>
     <row r="6">
@@ -513,7 +513,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>200334.830751398</v>
+        <v>199006.1601566482</v>
       </c>
     </row>
     <row r="9">
@@ -612,7 +612,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ethereum=25433093</t>
+          <t>ethereum=25433938</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:50+00:00</t>
+          <t>2026-07-15T11:29:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1069,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -1229,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1269,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1309,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1429,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1469,10 +1469,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1549,10 +1549,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0</v>
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1709,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -1749,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0</v>
@@ -1829,10 +1829,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0</v>
@@ -1909,10 +1909,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
@@ -1949,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>0</v>
@@ -2069,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0</v>
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>164694.33</v>
+        <v>163915.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>199006.1601566482</v>
+        <v>198227.4401566482</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>163915.61</v>
+        <v>191228.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>198227.4401566482</v>
+        <v>225540.3501566482</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>164694.33</v>
+        <v>191228.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>199006.1601566482</v>
+        <v>225540.3501566482</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -849,7 +849,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -511,130 +511,140 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>225540.3501566482</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ governance_accessibility_rewards (0.01 × SNR 2026-05 = 14066093.18595369152115625120 (sky_total generated sky_total))</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>140660.9318595369</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>366201.2820161852</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-06-30 (30 days)</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ethereum=25433938</t>
+          <t>2026-06-01 → 2026-06-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-15T11:29:30+00:00</t>
+          <t>ethereum=25433938</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:51:03+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
+++ b/settlements/skybase/2026-06/skybase_settlement_june_2026.xlsx
@@ -513,17 +513,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>+ governance_accessibility_rewards (0.01 × SNR 2026-05 = 14066093.18595369152115625120 (sky_total generated sky_total))</t>
+          <t>+ governance_accessibility_rewards (0.01 × SNR 2026-06 = 14875074.62937500082692341378 (sky_total generated sky_total))</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>140660.9318595369</v>
+        <v>148750.74629375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>366201.2820161852</v>
+        <v>374291.0964503983</v>
       </c>
     </row>
     <row r="10">
@@ -634,7 +634,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-05T23:51:03+00:00</t>
+          <t>2026-08-06T00:02:52+00:00</t>
         </is>
       </c>
     </row>
